--- a/03_study_selection/full_text/full_text_selection.xlsx
+++ b/03_study_selection/full_text/full_text_selection.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="437">
   <si>
     <t>title</t>
   </si>
@@ -685,9 +685,6 @@
   </si>
   <si>
     <t>Cited by: 6</t>
-  </si>
-  <si>
-    <t>Studies that propose, analyze, or evaluate methods, techniques, approaches, tools, or frameworks for ACC.</t>
   </si>
   <si>
     <t>Detecting and Resolving Coupling-Related Infrastructure as Code Based Architecture Smells in Microservice Deployments</t>
@@ -974,6 +971,9 @@
     <t>2835-7043</t>
   </si>
   <si>
+    <t>Studies that are clearly misaligned with the research questions, even if they mention ACC-related terms.</t>
+  </si>
+  <si>
     <t>Runtime Monitoring of Web Service Conversations</t>
   </si>
   <si>
@@ -1161,9 +1161,6 @@
   </si>
   <si>
     <t>co-evolution</t>
-  </si>
-  <si>
-    <t>Studies that are clearly misaligned with the research questions, even if they mention ACC-related terms.</t>
   </si>
   <si>
     <t>Consistency Management for Security Annotations for Continuous Verification</t>
@@ -2804,21 +2801,21 @@
         <v>223</v>
       </c>
       <c r="S22" s="5" t="s">
-        <v>88</v>
+        <v>34</v>
       </c>
       <c r="T22" s="5" t="s">
-        <v>224</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" ht="12.75" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>182</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>23</v>
@@ -2827,29 +2824,29 @@
         <v>24</v>
       </c>
       <c r="F23" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="H23" s="3" t="s">
         <v>228</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>229</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>51</v>
       </c>
       <c r="J23" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="K23" s="3" t="s">
         <v>230</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>231</v>
       </c>
       <c r="L23" s="3"/>
       <c r="M23" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="N23" s="3" t="s">
         <v>232</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>233</v>
       </c>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
@@ -2866,158 +2863,158 @@
     </row>
     <row r="24" ht="12.75" customHeight="1">
       <c r="A24" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>234</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>235</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>92</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F24" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="H24" s="3" t="s">
         <v>238</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>239</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>51</v>
       </c>
       <c r="J24" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="K24" s="3" t="s">
         <v>240</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>241</v>
       </c>
       <c r="L24" s="3"/>
       <c r="M24" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="N24" s="3" t="s">
         <v>242</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>243</v>
       </c>
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
       <c r="Q24" s="3"/>
       <c r="R24" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="S24" s="5" t="s">
-        <v>88</v>
+        <v>34</v>
       </c>
       <c r="T24" s="5" t="s">
-        <v>224</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" ht="12.75" customHeight="1">
       <c r="A25" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="C25" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>247</v>
-      </c>
       <c r="D25" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F25" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="H25" s="3" t="s">
         <v>249</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>250</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>28</v>
       </c>
       <c r="J25" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="K25" s="3" t="s">
         <v>251</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>252</v>
       </c>
       <c r="L25" s="3"/>
       <c r="M25" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="N25" s="3" t="s">
         <v>253</v>
-      </c>
-      <c r="N25" s="3" t="s">
-        <v>254</v>
       </c>
       <c r="O25" s="3"/>
       <c r="P25" s="3"/>
       <c r="Q25" s="3"/>
       <c r="R25" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="S25" s="5" t="s">
         <v>88</v>
       </c>
       <c r="T25" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="26" ht="12.75" customHeight="1">
       <c r="A26" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="C26" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>259</v>
-      </c>
       <c r="D26" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F26" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="H26" s="3" t="s">
         <v>261</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>262</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>28</v>
       </c>
       <c r="J26" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="K26" s="3" t="s">
         <v>263</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>264</v>
       </c>
       <c r="L26" s="3"/>
       <c r="M26" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="N26" s="3" t="s">
         <v>265</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>266</v>
       </c>
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
       <c r="Q26" s="3"/>
       <c r="R26" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="S26" s="5" t="s">
         <v>88</v>
@@ -3028,48 +3025,48 @@
     </row>
     <row r="27" ht="12.75" customHeight="1">
       <c r="A27" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="C27" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>270</v>
-      </c>
       <c r="D27" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G27" s="3"/>
       <c r="H27" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>51</v>
       </c>
       <c r="J27" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="K27" s="3" t="s">
         <v>273</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>274</v>
       </c>
       <c r="L27" s="3"/>
       <c r="M27" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="N27" s="3" t="s">
         <v>275</v>
-      </c>
-      <c r="N27" s="3" t="s">
-        <v>276</v>
       </c>
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
       <c r="Q27" s="3"/>
       <c r="R27" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="S27" s="5" t="s">
         <v>88</v>
@@ -3080,51 +3077,51 @@
     </row>
     <row r="28" ht="12.75" customHeight="1">
       <c r="A28" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="C28" s="3" t="s">
         <v>279</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>280</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E28" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="G28" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="H28" s="3" t="s">
         <v>282</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>283</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>28</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="K28" s="3"/>
       <c r="L28" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="M28" s="3"/>
       <c r="N28" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="O28" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="O28" s="3" t="s">
+      <c r="P28" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="P28" s="3" t="s">
+      <c r="Q28" s="3" t="s">
         <v>288</v>
-      </c>
-      <c r="Q28" s="3" t="s">
-        <v>289</v>
       </c>
       <c r="R28" s="3"/>
       <c r="S28" s="5" t="s">
@@ -3136,38 +3133,38 @@
     </row>
     <row r="29" ht="12.75" customHeight="1">
       <c r="A29" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>290</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>291</v>
       </c>
       <c r="C29" s="3"/>
       <c r="D29" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G29" s="3"/>
       <c r="H29" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I29" s="3"/>
       <c r="J29" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
       <c r="M29" s="3"/>
       <c r="N29" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="O29" s="3"/>
       <c r="P29" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Q29" s="3"/>
       <c r="R29" s="3"/>
@@ -3180,38 +3177,38 @@
     </row>
     <row r="30" ht="12.75" customHeight="1">
       <c r="A30" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>298</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>299</v>
       </c>
       <c r="C30" s="3"/>
       <c r="D30" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G30" s="3"/>
       <c r="H30" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="I30" s="3"/>
       <c r="J30" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
       <c r="M30" s="3"/>
       <c r="N30" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="O30" s="3"/>
       <c r="P30" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Q30" s="3"/>
       <c r="R30" s="3"/>
@@ -3224,46 +3221,46 @@
     </row>
     <row r="31" ht="12.75" customHeight="1">
       <c r="A31" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>306</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>307</v>
       </c>
       <c r="C31" s="3"/>
       <c r="D31" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G31" s="3"/>
       <c r="H31" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="I31" s="3"/>
       <c r="J31" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
       <c r="M31" s="3"/>
       <c r="N31" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="O31" s="3"/>
       <c r="P31" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q31" s="3"/>
       <c r="R31" s="3"/>
       <c r="S31" s="5" t="s">
-        <v>88</v>
+        <v>34</v>
       </c>
       <c r="T31" s="5" t="s">
-        <v>224</v>
+        <v>312</v>
       </c>
     </row>
     <row r="32" ht="12.75" customHeight="1">
@@ -3407,7 +3404,7 @@
       </c>
       <c r="C35" s="3"/>
       <c r="D35" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>336</v>
@@ -3625,41 +3622,41 @@
         <v>34</v>
       </c>
       <c r="T39" s="5" t="s">
-        <v>376</v>
+        <v>312</v>
       </c>
     </row>
     <row r="40" ht="12.75" customHeight="1">
       <c r="A40" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>377</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>378</v>
       </c>
       <c r="C40" s="3"/>
       <c r="D40" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>336</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="I40" s="3"/>
       <c r="J40" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="K40" s="3" t="s">
         <v>381</v>
-      </c>
-      <c r="K40" s="3" t="s">
-        <v>382</v>
       </c>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="O40" s="3" t="s">
         <v>367</v>
@@ -3671,15 +3668,15 @@
         <v>34</v>
       </c>
       <c r="T40" s="5" t="s">
-        <v>376</v>
+        <v>312</v>
       </c>
     </row>
     <row r="41" ht="12.75" customHeight="1">
       <c r="A41" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>384</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>385</v>
       </c>
       <c r="C41" s="3"/>
       <c r="D41" s="3" t="s">
@@ -3691,19 +3688,19 @@
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
       <c r="H41" s="3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="I41" s="3"/>
       <c r="J41" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="K41" s="3" t="s">
         <v>387</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>388</v>
       </c>
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
       <c r="N41" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="O41" s="3" t="s">
         <v>367</v>
@@ -3720,10 +3717,10 @@
     </row>
     <row r="42" ht="12.75" customHeight="1">
       <c r="A42" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>390</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>391</v>
       </c>
       <c r="C42" s="3"/>
       <c r="D42" s="3" t="s">
@@ -3733,26 +3730,26 @@
         <v>336</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G42" s="3"/>
       <c r="H42" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="I42" s="3"/>
       <c r="J42" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="K42" s="3" t="s">
         <v>394</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>395</v>
       </c>
       <c r="L42" s="3"/>
       <c r="M42" s="3"/>
       <c r="N42" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="O42" s="3" t="s">
         <v>396</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>397</v>
       </c>
       <c r="P42" s="3"/>
       <c r="Q42" s="3"/>
@@ -3766,13 +3763,13 @@
     </row>
     <row r="43" ht="12.75" customHeight="1">
       <c r="A43" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="C43" s="3" t="s">
         <v>399</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>400</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>69</v>
@@ -3781,31 +3778,31 @@
         <v>336</v>
       </c>
       <c r="F43" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="G43" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="G43" s="3" t="s">
+      <c r="H43" s="3" t="s">
         <v>402</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>403</v>
       </c>
       <c r="I43" s="3"/>
       <c r="J43" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="K43" s="3" t="s">
         <v>404</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>405</v>
       </c>
       <c r="L43" s="3"/>
       <c r="M43" s="3"/>
       <c r="N43" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="O43" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="O43" s="3" t="s">
+      <c r="P43" s="3" t="s">
         <v>407</v>
-      </c>
-      <c r="P43" s="3" t="s">
-        <v>408</v>
       </c>
       <c r="Q43" s="3"/>
       <c r="R43" s="3"/>
@@ -3813,41 +3810,41 @@
         <v>34</v>
       </c>
       <c r="T43" s="5" t="s">
-        <v>376</v>
+        <v>312</v>
       </c>
     </row>
     <row r="44" ht="12.75" customHeight="1">
       <c r="A44" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>409</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>410</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>336</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G44" s="3"/>
       <c r="H44" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="I44" s="3"/>
       <c r="J44" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="K44" s="3" t="s">
         <v>414</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>415</v>
       </c>
       <c r="L44" s="3"/>
       <c r="M44" s="3"/>
       <c r="N44" s="3" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="O44" s="3" t="s">
         <v>367</v>
@@ -3859,47 +3856,47 @@
         <v>34</v>
       </c>
       <c r="T44" s="5" t="s">
-        <v>376</v>
+        <v>312</v>
       </c>
     </row>
     <row r="45" ht="12.75" customHeight="1">
       <c r="A45" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="C45" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="C45" s="3" t="s">
-        <v>419</v>
-      </c>
       <c r="D45" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>336</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
       <c r="J45" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="K45" s="3" t="s">
         <v>421</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>422</v>
       </c>
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
       <c r="N45" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="O45" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="O45" s="3" t="s">
+      <c r="P45" s="3" t="s">
         <v>424</v>
-      </c>
-      <c r="P45" s="3" t="s">
-        <v>425</v>
       </c>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
@@ -3907,15 +3904,15 @@
         <v>34</v>
       </c>
       <c r="T45" s="5" t="s">
-        <v>376</v>
+        <v>312</v>
       </c>
     </row>
     <row r="46" ht="12.75" customHeight="1">
       <c r="A46" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>426</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>427</v>
       </c>
       <c r="C46" s="3"/>
       <c r="D46" s="3" t="s">
@@ -3925,11 +3922,11 @@
         <v>336</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="I46" s="3"/>
       <c r="J46" s="3"/>
@@ -3937,10 +3934,10 @@
       <c r="L46" s="3"/>
       <c r="M46" s="3"/>
       <c r="N46" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="O46" s="3" t="s">
         <v>430</v>
-      </c>
-      <c r="O46" s="3" t="s">
-        <v>431</v>
       </c>
       <c r="P46" s="3"/>
       <c r="Q46" s="3"/>
@@ -3949,15 +3946,15 @@
         <v>34</v>
       </c>
       <c r="T46" s="5" t="s">
-        <v>376</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" ht="12.75" customHeight="1">
       <c r="A47" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>432</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>433</v>
       </c>
       <c r="C47" s="3"/>
       <c r="D47" s="3" t="s">
@@ -3969,7 +3966,7 @@
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
       <c r="H47" s="3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="I47" s="3"/>
       <c r="J47" s="3"/>
@@ -3978,18 +3975,18 @@
       <c r="M47" s="3"/>
       <c r="N47" s="3"/>
       <c r="O47" s="3" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="P47" s="3"/>
       <c r="Q47" s="3"/>
       <c r="R47" s="3" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="S47" s="5" t="s">
         <v>34</v>
       </c>
       <c r="T47" s="5" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
